--- a/slots/resources/sample/playerLevelConfig.xlsx
+++ b/slots/resources/sample/playerLevelConfig.xlsx
@@ -6308,9 +6308,7 @@
       <c r="B204" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C204" s="8">
-        <v>6606304531300</v>
-      </c>
+      <c r="C204" s="8"/>
       <c r="D204" s="2">
         <v>0</v>
       </c>

--- a/slots/resources/sample/playerLevelConfig.xlsx
+++ b/slots/resources/sample/playerLevelConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="217">
   <si>
     <t>id</t>
   </si>
@@ -47,12 +47,18 @@
     <t>黑名单数量</t>
   </si>
   <si>
+    <t>道具奖励</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>long</t>
   </si>
   <si>
+    <t>map&lt;int{_}long&gt;{|}</t>
+  </si>
+  <si>
     <t>levelUpExp</t>
   </si>
   <si>
@@ -68,7 +74,13 @@
     <t>blockListNum</t>
   </si>
   <si>
+    <t>getItem</t>
+  </si>
+  <si>
     <t>等级1</t>
+  </si>
+  <si>
+    <t>1010101_1|1990000_10000</t>
   </si>
   <si>
     <t>等级2</t>
@@ -1302,7 +1314,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1314,6 +1326,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1645,17 +1660,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G204"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:H204"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.625" customWidth="1"/>
     <col min="3" max="3" width="21.5" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="15.375" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="6" max="7" width="12.625" customWidth="1"/>
+    <col min="8" max="8" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1675,63 +1691,72 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="6">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7">
         <v>25000</v>
       </c>
       <c r="D5" s="2">
@@ -1746,15 +1771,18 @@
       <c r="G5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="7">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8">
         <v>29500</v>
       </c>
       <c r="D6" s="2">
@@ -1769,15 +1797,18 @@
       <c r="G6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="7">
+        <v>19</v>
+      </c>
+      <c r="C7" s="8">
         <v>34800</v>
       </c>
       <c r="D7" s="2">
@@ -1792,15 +1823,18 @@
       <c r="G7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="7">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8">
         <v>41100</v>
       </c>
       <c r="D8" s="2">
@@ -1815,15 +1849,18 @@
       <c r="G8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="8">
+        <v>21</v>
+      </c>
+      <c r="C9" s="9">
         <v>48500</v>
       </c>
       <c r="D9" s="2">
@@ -1838,15 +1875,18 @@
       <c r="G9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="8">
+        <v>22</v>
+      </c>
+      <c r="C10" s="9">
         <v>57200</v>
       </c>
       <c r="D10" s="2">
@@ -1861,15 +1901,18 @@
       <c r="G10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="8">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9">
         <v>67500</v>
       </c>
       <c r="D11" s="2">
@@ -1884,15 +1927,18 @@
       <c r="G11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="8">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9">
         <v>79700</v>
       </c>
       <c r="D12" s="2">
@@ -1907,15 +1953,18 @@
       <c r="G12">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="8">
+        <v>25</v>
+      </c>
+      <c r="C13" s="9">
         <v>94000</v>
       </c>
       <c r="D13" s="2">
@@ -1930,15 +1979,18 @@
       <c r="G13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="8">
+        <v>26</v>
+      </c>
+      <c r="C14" s="9">
         <v>110900</v>
       </c>
       <c r="D14" s="2">
@@ -1953,15 +2005,18 @@
       <c r="G14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="8">
+        <v>27</v>
+      </c>
+      <c r="C15" s="9">
         <v>130900</v>
       </c>
       <c r="D15" s="2">
@@ -1976,15 +2031,18 @@
       <c r="G15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="8">
+        <v>28</v>
+      </c>
+      <c r="C16" s="9">
         <v>154500</v>
       </c>
       <c r="D16" s="2">
@@ -1999,15 +2057,18 @@
       <c r="G16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="8">
+        <v>29</v>
+      </c>
+      <c r="C17" s="9">
         <v>182300</v>
       </c>
       <c r="D17" s="2">
@@ -2022,15 +2083,18 @@
       <c r="G17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="8">
+        <v>30</v>
+      </c>
+      <c r="C18" s="9">
         <v>215100</v>
       </c>
       <c r="D18" s="2">
@@ -2045,15 +2109,18 @@
       <c r="G18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="8">
+        <v>31</v>
+      </c>
+      <c r="C19" s="9">
         <v>253800</v>
       </c>
       <c r="D19" s="2">
@@ -2068,15 +2135,18 @@
       <c r="G19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="8">
+        <v>32</v>
+      </c>
+      <c r="C20" s="9">
         <v>299500</v>
       </c>
       <c r="D20" s="2">
@@ -2091,15 +2161,18 @@
       <c r="G20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="8">
+        <v>33</v>
+      </c>
+      <c r="C21" s="9">
         <v>353400</v>
       </c>
       <c r="D21" s="2">
@@ -2114,15 +2187,18 @@
       <c r="G21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="8">
+        <v>34</v>
+      </c>
+      <c r="C22" s="9">
         <v>417000</v>
       </c>
       <c r="D22" s="2">
@@ -2137,15 +2213,18 @@
       <c r="G22">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="8">
+        <v>35</v>
+      </c>
+      <c r="C23" s="9">
         <v>492100</v>
       </c>
       <c r="D23" s="2">
@@ -2160,15 +2239,18 @@
       <c r="G23">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="8">
+        <v>36</v>
+      </c>
+      <c r="C24" s="9">
         <v>580700</v>
       </c>
       <c r="D24" s="2">
@@ -2183,15 +2265,18 @@
       <c r="G24">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="8">
+        <v>37</v>
+      </c>
+      <c r="C25" s="9">
         <v>673600</v>
       </c>
       <c r="D25" s="2">
@@ -2206,15 +2291,18 @@
       <c r="G25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="8">
+        <v>38</v>
+      </c>
+      <c r="C26" s="9">
         <v>781400</v>
       </c>
       <c r="D26" s="2">
@@ -2229,15 +2317,18 @@
       <c r="G26">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="8">
+        <v>39</v>
+      </c>
+      <c r="C27" s="9">
         <v>906400</v>
       </c>
       <c r="D27" s="2">
@@ -2252,15 +2343,18 @@
       <c r="G27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="8">
+        <v>40</v>
+      </c>
+      <c r="C28" s="9">
         <v>1051400</v>
       </c>
       <c r="D28" s="2">
@@ -2275,15 +2369,18 @@
       <c r="G28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="8">
+        <v>41</v>
+      </c>
+      <c r="C29" s="9">
         <v>1219600</v>
       </c>
       <c r="D29" s="2">
@@ -2298,15 +2395,18 @@
       <c r="G29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="8">
+        <v>42</v>
+      </c>
+      <c r="C30" s="9">
         <v>1414700</v>
       </c>
       <c r="D30" s="2">
@@ -2321,15 +2421,18 @@
       <c r="G30">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="8">
+        <v>43</v>
+      </c>
+      <c r="C31" s="9">
         <v>1641100</v>
       </c>
       <c r="D31" s="2">
@@ -2344,15 +2447,18 @@
       <c r="G31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="8">
+        <v>44</v>
+      </c>
+      <c r="C32" s="9">
         <v>1903700</v>
       </c>
       <c r="D32" s="2">
@@ -2367,15 +2473,18 @@
       <c r="G32">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="8">
+        <v>45</v>
+      </c>
+      <c r="C33" s="9">
         <v>2208300</v>
       </c>
       <c r="D33" s="2">
@@ -2390,15 +2499,18 @@
       <c r="G33">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="8">
+        <v>46</v>
+      </c>
+      <c r="C34" s="9">
         <v>2561600</v>
       </c>
       <c r="D34" s="2">
@@ -2413,15 +2525,18 @@
       <c r="G34">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="8">
+        <v>47</v>
+      </c>
+      <c r="C35" s="9">
         <v>2971500</v>
       </c>
       <c r="D35" s="2">
@@ -2436,15 +2551,18 @@
       <c r="G35">
         <v>10</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="8">
+        <v>48</v>
+      </c>
+      <c r="C36" s="9">
         <v>3446900</v>
       </c>
       <c r="D36" s="2">
@@ -2459,15 +2577,18 @@
       <c r="G36">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="8">
+        <v>49</v>
+      </c>
+      <c r="C37" s="9">
         <v>3998400</v>
       </c>
       <c r="D37" s="2">
@@ -2482,15 +2603,18 @@
       <c r="G37">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="8">
+        <v>50</v>
+      </c>
+      <c r="C38" s="9">
         <v>4638100</v>
       </c>
       <c r="D38" s="2">
@@ -2505,15 +2629,18 @@
       <c r="G38">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="8">
+        <v>51</v>
+      </c>
+      <c r="C39" s="9">
         <v>5380200</v>
       </c>
       <c r="D39" s="2">
@@ -2528,15 +2655,18 @@
       <c r="G39">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1">
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" s="8">
+        <v>52</v>
+      </c>
+      <c r="C40" s="9">
         <v>6241000</v>
       </c>
       <c r="D40" s="2">
@@ -2551,15 +2681,18 @@
       <c r="G40">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1">
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="8">
+        <v>53</v>
+      </c>
+      <c r="C41" s="9">
         <v>7239600</v>
       </c>
       <c r="D41" s="2">
@@ -2574,15 +2707,18 @@
       <c r="G41">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1">
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="8">
+        <v>54</v>
+      </c>
+      <c r="C42" s="9">
         <v>8397900</v>
       </c>
       <c r="D42" s="2">
@@ -2597,15 +2733,18 @@
       <c r="G42">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1">
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="8">
+        <v>55</v>
+      </c>
+      <c r="C43" s="9">
         <v>9741600</v>
       </c>
       <c r="D43" s="2">
@@ -2620,15 +2759,18 @@
       <c r="G43">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1">
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="8">
+        <v>56</v>
+      </c>
+      <c r="C44" s="9">
         <v>11300300</v>
       </c>
       <c r="D44" s="2">
@@ -2643,15 +2785,18 @@
       <c r="G44">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1">
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="8">
+        <v>57</v>
+      </c>
+      <c r="C45" s="9">
         <v>13108300</v>
       </c>
       <c r="D45" s="2">
@@ -2666,15 +2811,18 @@
       <c r="G45">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1">
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="8">
+        <v>58</v>
+      </c>
+      <c r="C46" s="9">
         <v>15205600</v>
       </c>
       <c r="D46" s="2">
@@ -2689,15 +2837,18 @@
       <c r="G46">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1">
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="8">
+        <v>59</v>
+      </c>
+      <c r="C47" s="9">
         <v>17638500</v>
       </c>
       <c r="D47" s="2">
@@ -2712,15 +2863,18 @@
       <c r="G47">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1">
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="8">
+        <v>60</v>
+      </c>
+      <c r="C48" s="9">
         <v>20460700</v>
       </c>
       <c r="D48" s="2">
@@ -2735,15 +2889,18 @@
       <c r="G48">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1">
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="8">
+        <v>61</v>
+      </c>
+      <c r="C49" s="9">
         <v>23734400</v>
       </c>
       <c r="D49" s="2">
@@ -2758,15 +2915,18 @@
       <c r="G49">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:7">
+      <c r="H49" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="1">
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="8">
+        <v>62</v>
+      </c>
+      <c r="C50" s="9">
         <v>27531900</v>
       </c>
       <c r="D50" s="2">
@@ -2781,15 +2941,18 @@
       <c r="G50">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
+      <c r="H50" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="1">
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="8">
+        <v>63</v>
+      </c>
+      <c r="C51" s="9">
         <v>31937000</v>
       </c>
       <c r="D51" s="2">
@@ -2804,15 +2967,18 @@
       <c r="G51">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:7">
+      <c r="H51" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="1">
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" s="8">
+        <v>64</v>
+      </c>
+      <c r="C52" s="9">
         <v>37046900</v>
       </c>
       <c r="D52" s="2">
@@ -2827,15 +2993,18 @@
       <c r="G52">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:7">
+      <c r="H52" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="1">
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="8">
+        <v>65</v>
+      </c>
+      <c r="C53" s="9">
         <v>42974400</v>
       </c>
       <c r="D53" s="2">
@@ -2850,15 +3019,18 @@
       <c r="G53">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:7">
+      <c r="H53" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="1">
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C54" s="8">
+        <v>66</v>
+      </c>
+      <c r="C54" s="9">
         <v>49850300</v>
       </c>
       <c r="D54" s="2">
@@ -2873,15 +3045,18 @@
       <c r="G54">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:7">
+      <c r="H54" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="1">
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" s="8">
+        <v>67</v>
+      </c>
+      <c r="C55" s="9">
         <v>56829300</v>
       </c>
       <c r="D55" s="2">
@@ -2896,15 +3071,18 @@
       <c r="G55">
         <v>10</v>
       </c>
-    </row>
-    <row r="56" spans="1:7">
+      <c r="H55" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="1">
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C56" s="8">
+        <v>68</v>
+      </c>
+      <c r="C56" s="9">
         <v>64785400</v>
       </c>
       <c r="D56" s="2">
@@ -2919,15 +3097,18 @@
       <c r="G56">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="H56" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="1">
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="8">
+        <v>69</v>
+      </c>
+      <c r="C57" s="9">
         <v>73855400</v>
       </c>
       <c r="D57" s="2">
@@ -2942,15 +3123,18 @@
       <c r="G57">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:7">
+      <c r="H57" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="1">
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C58" s="8">
+        <v>70</v>
+      </c>
+      <c r="C58" s="9">
         <v>84195200</v>
       </c>
       <c r="D58" s="2">
@@ -2965,15 +3149,18 @@
       <c r="G58">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:7">
+      <c r="H58" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="1">
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="8">
+        <v>71</v>
+      </c>
+      <c r="C59" s="9">
         <v>95982500</v>
       </c>
       <c r="D59" s="2">
@@ -2988,15 +3175,18 @@
       <c r="G59">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:7">
+      <c r="H59" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="1">
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="8">
+        <v>72</v>
+      </c>
+      <c r="C60" s="9">
         <v>109420100</v>
       </c>
       <c r="D60" s="2">
@@ -3011,15 +3201,18 @@
       <c r="G60">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:7">
+      <c r="H60" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="1">
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="8">
+        <v>73</v>
+      </c>
+      <c r="C61" s="9">
         <v>124738900</v>
       </c>
       <c r="D61" s="2">
@@ -3034,15 +3227,18 @@
       <c r="G61">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:7">
+      <c r="H61" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="8">
+        <v>74</v>
+      </c>
+      <c r="C62" s="9">
         <v>142202300</v>
       </c>
       <c r="D62" s="2">
@@ -3057,15 +3253,18 @@
       <c r="G62">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:7">
+      <c r="H62" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="1">
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="8">
+        <v>75</v>
+      </c>
+      <c r="C63" s="9">
         <v>162110600</v>
       </c>
       <c r="D63" s="2">
@@ -3080,15 +3279,18 @@
       <c r="G63">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
+      <c r="H63" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C64" s="8">
+        <v>76</v>
+      </c>
+      <c r="C64" s="9">
         <v>184806100</v>
       </c>
       <c r="D64" s="2">
@@ -3103,15 +3305,18 @@
       <c r="G64">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="H64" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="1">
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="8">
+        <v>77</v>
+      </c>
+      <c r="C65" s="9">
         <v>210679000</v>
       </c>
       <c r="D65" s="2">
@@ -3126,15 +3331,18 @@
       <c r="G65">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:7">
+      <c r="H65" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="1">
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" s="8">
+        <v>78</v>
+      </c>
+      <c r="C66" s="9">
         <v>240174100</v>
       </c>
       <c r="D66" s="2">
@@ -3149,15 +3357,18 @@
       <c r="G66">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="H66" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="1">
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" s="8">
+        <v>79</v>
+      </c>
+      <c r="C67" s="9">
         <v>273798500</v>
       </c>
       <c r="D67" s="2">
@@ -3172,15 +3383,18 @@
       <c r="G67">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1">
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" s="8">
+        <v>80</v>
+      </c>
+      <c r="C68" s="9">
         <v>312130300</v>
       </c>
       <c r="D68" s="2">
@@ -3195,15 +3409,18 @@
       <c r="G68">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1">
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C69" s="8">
+        <v>81</v>
+      </c>
+      <c r="C69" s="9">
         <v>355828500</v>
       </c>
       <c r="D69" s="2">
@@ -3218,15 +3435,18 @@
       <c r="G69">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1">
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="8">
+        <v>82</v>
+      </c>
+      <c r="C70" s="9">
         <v>405644500</v>
       </c>
       <c r="D70" s="2">
@@ -3241,15 +3461,18 @@
       <c r="G70">
         <v>10</v>
       </c>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1">
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C71" s="8">
+        <v>83</v>
+      </c>
+      <c r="C71" s="9">
         <v>462434700</v>
       </c>
       <c r="D71" s="2">
@@ -3264,15 +3487,18 @@
       <c r="G71">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1">
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" s="8">
+        <v>84</v>
+      </c>
+      <c r="C72" s="9">
         <v>527175600</v>
       </c>
       <c r="D72" s="2">
@@ -3287,15 +3513,18 @@
       <c r="G72">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1">
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C73" s="8">
+        <v>85</v>
+      </c>
+      <c r="C73" s="9">
         <v>600980200</v>
       </c>
       <c r="D73" s="2">
@@ -3310,15 +3539,18 @@
       <c r="G73">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1">
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" s="8">
+        <v>86</v>
+      </c>
+      <c r="C74" s="9">
         <v>685117400</v>
       </c>
       <c r="D74" s="2">
@@ -3333,15 +3565,18 @@
       <c r="G74">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1">
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="8">
+        <v>87</v>
+      </c>
+      <c r="C75" s="9">
         <v>781033800</v>
       </c>
       <c r="D75" s="2">
@@ -3356,15 +3591,18 @@
       <c r="G75">
         <v>10</v>
       </c>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="1">
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76" s="8">
+        <v>88</v>
+      </c>
+      <c r="C76" s="9">
         <v>890378500</v>
       </c>
       <c r="D76" s="2">
@@ -3379,15 +3617,18 @@
       <c r="G76">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1">
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C77" s="8">
+        <v>89</v>
+      </c>
+      <c r="C77" s="9">
         <v>1015031500</v>
       </c>
       <c r="D77" s="2">
@@ -3402,15 +3643,18 @@
       <c r="G77">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="1">
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" s="8">
+        <v>90</v>
+      </c>
+      <c r="C78" s="9">
         <v>1157135900</v>
       </c>
       <c r="D78" s="2">
@@ -3425,15 +3669,18 @@
       <c r="G78">
         <v>10</v>
       </c>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="1">
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" s="8">
+        <v>91</v>
+      </c>
+      <c r="C79" s="9">
         <v>1319134900</v>
       </c>
       <c r="D79" s="2">
@@ -3448,15 +3695,18 @@
       <c r="G79">
         <v>10</v>
       </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1">
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C80" s="8">
+        <v>92</v>
+      </c>
+      <c r="C80" s="9">
         <v>1503813800</v>
       </c>
       <c r="D80" s="2">
@@ -3471,15 +3721,18 @@
       <c r="G80">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1">
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="8">
+        <v>93</v>
+      </c>
+      <c r="C81" s="9">
         <v>1714347700</v>
       </c>
       <c r="D81" s="2">
@@ -3494,15 +3747,18 @@
       <c r="G81">
         <v>10</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="1">
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" s="8">
+        <v>94</v>
+      </c>
+      <c r="C82" s="9">
         <v>1954356400</v>
       </c>
       <c r="D82" s="2">
@@ -3517,15 +3773,18 @@
       <c r="G82">
         <v>10</v>
       </c>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="1">
         <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" s="8">
+        <v>95</v>
+      </c>
+      <c r="C83" s="9">
         <v>2227966300</v>
       </c>
       <c r="D83" s="2">
@@ -3540,15 +3799,18 @@
       <c r="G83">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="H83" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="1">
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C84" s="8">
+        <v>96</v>
+      </c>
+      <c r="C84" s="9">
         <v>2539881600</v>
       </c>
       <c r="D84" s="2">
@@ -3563,15 +3825,18 @@
       <c r="G84">
         <v>10</v>
       </c>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="1">
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C85" s="8">
+        <v>97</v>
+      </c>
+      <c r="C85" s="9">
         <v>2844667400</v>
       </c>
       <c r="D85" s="2">
@@ -3586,15 +3851,18 @@
       <c r="G85">
         <v>10</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1">
         <v>82</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C86" s="8">
+        <v>98</v>
+      </c>
+      <c r="C86" s="9">
         <v>3186027500</v>
       </c>
       <c r="D86" s="2">
@@ -3609,15 +3877,18 @@
       <c r="G86">
         <v>10</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1">
         <v>83</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C87" s="8">
+        <v>99</v>
+      </c>
+      <c r="C87" s="9">
         <v>3568350800</v>
       </c>
       <c r="D87" s="2">
@@ -3632,15 +3903,18 @@
       <c r="G87">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="H87" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="1">
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C88" s="8">
+        <v>100</v>
+      </c>
+      <c r="C88" s="9">
         <v>3996552900</v>
       </c>
       <c r="D88" s="2">
@@ -3655,15 +3929,18 @@
       <c r="G88">
         <v>10</v>
       </c>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="H88" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="1">
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C89" s="8">
+        <v>101</v>
+      </c>
+      <c r="C89" s="9">
         <v>4476139200</v>
       </c>
       <c r="D89" s="2">
@@ -3678,15 +3955,18 @@
       <c r="G89">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H89" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="1">
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C90" s="8">
+        <v>102</v>
+      </c>
+      <c r="C90" s="9">
         <v>5013275900</v>
       </c>
       <c r="D90" s="2">
@@ -3701,15 +3981,18 @@
       <c r="G90">
         <v>10</v>
       </c>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="H90" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="1">
         <v>87</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C91" s="8">
+        <v>103</v>
+      </c>
+      <c r="C91" s="9">
         <v>5614869000</v>
       </c>
       <c r="D91" s="2">
@@ -3724,15 +4007,18 @@
       <c r="G91">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="H91" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="1">
         <v>88</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C92" s="8">
+        <v>104</v>
+      </c>
+      <c r="C92" s="9">
         <v>6288653300</v>
       </c>
       <c r="D92" s="2">
@@ -3747,15 +4033,18 @@
       <c r="G92">
         <v>10</v>
       </c>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="H92" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="1">
         <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C93" s="8">
+        <v>105</v>
+      </c>
+      <c r="C93" s="9">
         <v>7043291700</v>
       </c>
       <c r="D93" s="2">
@@ -3770,15 +4059,18 @@
       <c r="G93">
         <v>10</v>
       </c>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="H93" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="1">
         <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C94" s="8">
+        <v>106</v>
+      </c>
+      <c r="C94" s="9">
         <v>7888486700</v>
       </c>
       <c r="D94" s="2">
@@ -3793,15 +4085,18 @@
       <c r="G94">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="H94" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="1">
         <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C95" s="8">
+        <v>107</v>
+      </c>
+      <c r="C95" s="9">
         <v>8835105100</v>
       </c>
       <c r="D95" s="2">
@@ -3816,15 +4111,18 @@
       <c r="G95">
         <v>10</v>
       </c>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="H95" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="1">
         <v>92</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C96" s="8">
+        <v>108</v>
+      </c>
+      <c r="C96" s="9">
         <v>9895317700</v>
       </c>
       <c r="D96" s="2">
@@ -3839,15 +4137,18 @@
       <c r="G96">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="H96" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="1">
         <v>93</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C97" s="8">
+        <v>109</v>
+      </c>
+      <c r="C97" s="9">
         <v>11082755800</v>
       </c>
       <c r="D97" s="2">
@@ -3862,15 +4163,18 @@
       <c r="G97">
         <v>10</v>
       </c>
-    </row>
-    <row r="98" spans="1:7">
+      <c r="H97" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1">
         <v>94</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C98" s="8">
+        <v>110</v>
+      </c>
+      <c r="C98" s="9">
         <v>12412686500</v>
       </c>
       <c r="D98" s="2">
@@ -3885,15 +4189,18 @@
       <c r="G98">
         <v>10</v>
       </c>
-    </row>
-    <row r="99" spans="1:7">
+      <c r="H98" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="1">
         <v>95</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C99" s="8">
+        <v>111</v>
+      </c>
+      <c r="C99" s="9">
         <v>13902208900</v>
       </c>
       <c r="D99" s="2">
@@ -3908,15 +4215,18 @@
       <c r="G99">
         <v>10</v>
       </c>
-    </row>
-    <row r="100" spans="1:7">
+      <c r="H99" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="1">
         <v>96</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C100" s="8">
+        <v>112</v>
+      </c>
+      <c r="C100" s="9">
         <v>15570474000</v>
       </c>
       <c r="D100" s="2">
@@ -3931,15 +4241,18 @@
       <c r="G100">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="H100" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" s="1">
         <v>97</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C101" s="8">
+        <v>113</v>
+      </c>
+      <c r="C101" s="9">
         <v>17438930900</v>
       </c>
       <c r="D101" s="2">
@@ -3954,15 +4267,18 @@
       <c r="G101">
         <v>10</v>
       </c>
-    </row>
-    <row r="102" spans="1:7">
+      <c r="H101" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" s="1">
         <v>98</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C102" s="8">
+        <v>114</v>
+      </c>
+      <c r="C102" s="9">
         <v>19531602600</v>
       </c>
       <c r="D102" s="2">
@@ -3977,15 +4293,18 @@
       <c r="G102">
         <v>10</v>
       </c>
-    </row>
-    <row r="103" spans="1:7">
+      <c r="H102" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" s="1">
         <v>99</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C103" s="8">
+        <v>115</v>
+      </c>
+      <c r="C103" s="9">
         <v>21875394900</v>
       </c>
       <c r="D103" s="2">
@@ -4000,15 +4319,18 @@
       <c r="G103">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:7">
+      <c r="H103" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" s="1">
         <v>100</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C104" s="8">
+        <v>116</v>
+      </c>
+      <c r="C104" s="9">
         <v>24500442300</v>
       </c>
       <c r="D104" s="2">
@@ -4023,15 +4345,18 @@
       <c r="G104">
         <v>10</v>
       </c>
-    </row>
-    <row r="105" spans="1:7">
+      <c r="H104" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="1">
         <v>101</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C105" s="8">
+        <v>117</v>
+      </c>
+      <c r="C105" s="9">
         <v>26950486500</v>
       </c>
       <c r="D105" s="2">
@@ -4046,15 +4371,18 @@
       <c r="G105">
         <v>10</v>
       </c>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="H105" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" s="1">
         <v>102</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C106" s="8">
+        <v>118</v>
+      </c>
+      <c r="C106" s="9">
         <v>29645535200</v>
       </c>
       <c r="D106" s="2">
@@ -4069,15 +4397,18 @@
       <c r="G106">
         <v>10</v>
       </c>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="H106" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" s="1">
         <v>103</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C107" s="8">
+        <v>119</v>
+      </c>
+      <c r="C107" s="9">
         <v>32610088700</v>
       </c>
       <c r="D107" s="2">
@@ -4092,15 +4423,18 @@
       <c r="G107">
         <v>10</v>
       </c>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="H107" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="1">
         <v>104</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C108" s="8">
+        <v>120</v>
+      </c>
+      <c r="C108" s="9">
         <v>35871097600</v>
       </c>
       <c r="D108" s="2">
@@ -4115,15 +4449,18 @@
       <c r="G108">
         <v>10</v>
       </c>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="H108" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="1">
         <v>105</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C109" s="8">
+        <v>121</v>
+      </c>
+      <c r="C109" s="9">
         <v>39458207400</v>
       </c>
       <c r="D109" s="2">
@@ -4138,15 +4475,18 @@
       <c r="G109">
         <v>10</v>
       </c>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="H109" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="1">
         <v>106</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C110" s="8">
+        <v>122</v>
+      </c>
+      <c r="C110" s="9">
         <v>43404028100</v>
       </c>
       <c r="D110" s="2">
@@ -4161,15 +4501,18 @@
       <c r="G110">
         <v>10</v>
       </c>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="H110" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="1">
         <v>107</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C111" s="8">
+        <v>123</v>
+      </c>
+      <c r="C111" s="9">
         <v>47744430900</v>
       </c>
       <c r="D111" s="2">
@@ -4184,15 +4527,18 @@
       <c r="G111">
         <v>10</v>
       </c>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="H111" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" s="1">
         <v>108</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C112" s="8">
+        <v>124</v>
+      </c>
+      <c r="C112" s="9">
         <v>52518874000</v>
       </c>
       <c r="D112" s="2">
@@ -4207,15 +4553,18 @@
       <c r="G112">
         <v>10</v>
       </c>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="H112" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" s="1">
         <v>109</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C113" s="8">
+        <v>125</v>
+      </c>
+      <c r="C113" s="9">
         <v>57770761400</v>
       </c>
       <c r="D113" s="2">
@@ -4230,15 +4579,18 @@
       <c r="G113">
         <v>10</v>
       </c>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="H113" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" s="1">
         <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C114" s="8">
+        <v>126</v>
+      </c>
+      <c r="C114" s="9">
         <v>63547837500</v>
       </c>
       <c r="D114" s="2">
@@ -4253,15 +4605,18 @@
       <c r="G114">
         <v>10</v>
       </c>
-    </row>
-    <row r="115" spans="1:7">
+      <c r="H114" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" s="1">
         <v>111</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C115" s="8">
+        <v>127</v>
+      </c>
+      <c r="C115" s="9">
         <v>69902621300</v>
       </c>
       <c r="D115" s="2">
@@ -4276,15 +4631,18 @@
       <c r="G115">
         <v>10</v>
       </c>
-    </row>
-    <row r="116" spans="1:7">
+      <c r="H115" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" s="1">
         <v>112</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C116" s="8">
+        <v>128</v>
+      </c>
+      <c r="C116" s="9">
         <v>76892883400</v>
       </c>
       <c r="D116" s="2">
@@ -4299,15 +4657,18 @@
       <c r="G116">
         <v>10</v>
       </c>
-    </row>
-    <row r="117" spans="1:7">
+      <c r="H116" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" s="1">
         <v>113</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C117" s="8">
+        <v>129</v>
+      </c>
+      <c r="C117" s="9">
         <v>84582171700</v>
       </c>
       <c r="D117" s="2">
@@ -4322,15 +4683,18 @@
       <c r="G117">
         <v>10</v>
       </c>
-    </row>
-    <row r="118" spans="1:7">
+      <c r="H117" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" s="1">
         <v>114</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C118" s="8">
+        <v>130</v>
+      </c>
+      <c r="C118" s="9">
         <v>93040388900</v>
       </c>
       <c r="D118" s="2">
@@ -4345,15 +4709,18 @@
       <c r="G118">
         <v>10</v>
       </c>
-    </row>
-    <row r="119" spans="1:7">
+      <c r="H118" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" s="1">
         <v>115</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C119" s="8">
+        <v>131</v>
+      </c>
+      <c r="C119" s="9">
         <v>102344427800</v>
       </c>
       <c r="D119" s="2">
@@ -4368,15 +4735,18 @@
       <c r="G119">
         <v>10</v>
       </c>
-    </row>
-    <row r="120" spans="1:7">
+      <c r="H119" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" s="1">
         <v>116</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C120" s="8">
+        <v>132</v>
+      </c>
+      <c r="C120" s="9">
         <v>112578870600</v>
       </c>
       <c r="D120" s="2">
@@ -4391,15 +4761,18 @@
       <c r="G120">
         <v>10</v>
       </c>
-    </row>
-    <row r="121" spans="1:7">
+      <c r="H120" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" s="1">
         <v>117</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C121" s="8">
+        <v>133</v>
+      </c>
+      <c r="C121" s="9">
         <v>123836757700</v>
       </c>
       <c r="D121" s="2">
@@ -4414,15 +4787,18 @@
       <c r="G121">
         <v>10</v>
       </c>
-    </row>
-    <row r="122" spans="1:7">
+      <c r="H121" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" s="1">
         <v>118</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C122" s="8">
+        <v>134</v>
+      </c>
+      <c r="C122" s="9">
         <v>136220433500</v>
       </c>
       <c r="D122" s="2">
@@ -4437,15 +4813,18 @@
       <c r="G122">
         <v>10</v>
       </c>
-    </row>
-    <row r="123" spans="1:7">
+      <c r="H122" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" s="1">
         <v>119</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C123" s="8">
+        <v>135</v>
+      </c>
+      <c r="C123" s="9">
         <v>149842476900</v>
       </c>
       <c r="D123" s="2">
@@ -4460,15 +4839,18 @@
       <c r="G123">
         <v>10</v>
       </c>
-    </row>
-    <row r="124" spans="1:7">
+      <c r="H123" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" s="1">
         <v>120</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C124" s="8">
+        <v>136</v>
+      </c>
+      <c r="C124" s="9">
         <v>164826724600</v>
       </c>
       <c r="D124" s="2">
@@ -4483,15 +4865,18 @@
       <c r="G124">
         <v>10</v>
       </c>
-    </row>
-    <row r="125" spans="1:7">
+      <c r="H124" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" s="1">
         <v>121</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C125" s="8">
+        <v>137</v>
+      </c>
+      <c r="C125" s="9">
         <v>178012862600</v>
       </c>
       <c r="D125" s="2">
@@ -4506,15 +4891,18 @@
       <c r="G125">
         <v>10</v>
       </c>
-    </row>
-    <row r="126" spans="1:7">
+      <c r="H125" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" s="1">
         <v>122</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C126" s="8">
+        <v>138</v>
+      </c>
+      <c r="C126" s="9">
         <v>192253891600</v>
       </c>
       <c r="D126" s="2">
@@ -4529,15 +4917,18 @@
       <c r="G126">
         <v>10</v>
       </c>
-    </row>
-    <row r="127" spans="1:7">
+      <c r="H126" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="1">
         <v>123</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C127" s="8">
+        <v>139</v>
+      </c>
+      <c r="C127" s="9">
         <v>207634202900</v>
       </c>
       <c r="D127" s="2">
@@ -4552,15 +4943,18 @@
       <c r="G127">
         <v>10</v>
       </c>
-    </row>
-    <row r="128" spans="1:7">
+      <c r="H127" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" s="1">
         <v>124</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C128" s="8">
+        <v>140</v>
+      </c>
+      <c r="C128" s="9">
         <v>224244939100</v>
       </c>
       <c r="D128" s="2">
@@ -4575,15 +4969,18 @@
       <c r="G128">
         <v>10</v>
       </c>
-    </row>
-    <row r="129" spans="1:7">
+      <c r="H128" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>125</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C129" s="8">
+        <v>141</v>
+      </c>
+      <c r="C129" s="9">
         <v>242184534200</v>
       </c>
       <c r="D129" s="2">
@@ -4598,15 +4995,18 @@
       <c r="G129">
         <v>10</v>
       </c>
-    </row>
-    <row r="130" spans="1:7">
+      <c r="H129" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="1">
         <v>126</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C130" s="8">
+        <v>142</v>
+      </c>
+      <c r="C130" s="9">
         <v>261559296900</v>
       </c>
       <c r="D130" s="2">
@@ -4621,15 +5021,18 @@
       <c r="G130">
         <v>10</v>
       </c>
-    </row>
-    <row r="131" spans="1:7">
+      <c r="H130" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="1">
         <v>127</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C131" s="8">
+        <v>143</v>
+      </c>
+      <c r="C131" s="9">
         <v>282484040700</v>
       </c>
       <c r="D131" s="2">
@@ -4644,15 +5047,18 @@
       <c r="G131">
         <v>10</v>
       </c>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="H131" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>128</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C132" s="8">
+        <v>144</v>
+      </c>
+      <c r="C132" s="9">
         <v>305082764000</v>
       </c>
       <c r="D132" s="2">
@@ -4667,15 +5073,18 @@
       <c r="G132">
         <v>10</v>
       </c>
-    </row>
-    <row r="133" spans="1:7">
+      <c r="H132" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>129</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C133" s="8">
+        <v>145</v>
+      </c>
+      <c r="C133" s="9">
         <v>329489385100</v>
       </c>
       <c r="D133" s="2">
@@ -4690,15 +5099,18 @@
       <c r="G133">
         <v>10</v>
       </c>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="H133" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>130</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C134" s="8">
+        <v>146</v>
+      </c>
+      <c r="C134" s="9">
         <v>355848535900</v>
       </c>
       <c r="D134" s="2">
@@ -4713,15 +5125,18 @@
       <c r="G134">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:7">
+      <c r="H134" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>131</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C135" s="8">
+        <v>147</v>
+      </c>
+      <c r="C135" s="9">
         <v>384316418800</v>
       </c>
       <c r="D135" s="2">
@@ -4736,15 +5151,18 @@
       <c r="G135">
         <v>10</v>
       </c>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="H135" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>132</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C136" s="8">
+        <v>148</v>
+      </c>
+      <c r="C136" s="9">
         <v>415061732300</v>
       </c>
       <c r="D136" s="2">
@@ -4759,15 +5177,18 @@
       <c r="G136">
         <v>10</v>
       </c>
-    </row>
-    <row r="137" spans="1:7">
+      <c r="H136" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>133</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C137" s="8">
+        <v>149</v>
+      </c>
+      <c r="C137" s="9">
         <v>448266670900</v>
       </c>
       <c r="D137" s="2">
@@ -4782,15 +5203,18 @@
       <c r="G137">
         <v>10</v>
       </c>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="H137" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="1">
         <v>134</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C138" s="8">
+        <v>150</v>
+      </c>
+      <c r="C138" s="9">
         <v>484128004600</v>
       </c>
       <c r="D138" s="2">
@@ -4805,15 +5229,18 @@
       <c r="G138">
         <v>10</v>
       </c>
-    </row>
-    <row r="139" spans="1:7">
+      <c r="H138" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="1">
         <v>135</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C139" s="8">
+        <v>151</v>
+      </c>
+      <c r="C139" s="9">
         <v>522858245000</v>
       </c>
       <c r="D139" s="2">
@@ -4828,15 +5255,18 @@
       <c r="G139">
         <v>10</v>
       </c>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="H139" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="1">
         <v>136</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C140" s="8">
+        <v>152</v>
+      </c>
+      <c r="C140" s="9">
         <v>564686904600</v>
       </c>
       <c r="D140" s="2">
@@ -4851,15 +5281,18 @@
       <c r="G140">
         <v>10</v>
       </c>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="H140" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="1">
         <v>137</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C141" s="8">
+        <v>153</v>
+      </c>
+      <c r="C141" s="9">
         <v>609861857000</v>
       </c>
       <c r="D141" s="2">
@@ -4874,15 +5307,18 @@
       <c r="G141">
         <v>10</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="1">
         <v>138</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C142" s="8">
+        <v>154</v>
+      </c>
+      <c r="C142" s="9">
         <v>658650805600</v>
       </c>
       <c r="D142" s="2">
@@ -4897,15 +5333,18 @@
       <c r="G142">
         <v>10</v>
       </c>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="1">
         <v>139</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C143" s="8">
+        <v>155</v>
+      </c>
+      <c r="C143" s="9">
         <v>711342870000</v>
       </c>
       <c r="D143" s="2">
@@ -4920,15 +5359,18 @@
       <c r="G143">
         <v>10</v>
       </c>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="1">
         <v>140</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C144" s="8">
+        <v>156</v>
+      </c>
+      <c r="C144" s="9">
         <v>768250299600</v>
       </c>
       <c r="D144" s="2">
@@ -4943,15 +5385,18 @@
       <c r="G144">
         <v>10</v>
       </c>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="H144" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="1">
         <v>141</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C145" s="8">
+        <v>157</v>
+      </c>
+      <c r="C145" s="9">
         <v>814345317600</v>
       </c>
       <c r="D145" s="2">
@@ -4966,15 +5411,18 @@
       <c r="G145">
         <v>10</v>
       </c>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="1">
         <v>142</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C146" s="8">
+        <v>158</v>
+      </c>
+      <c r="C146" s="9">
         <v>863206036700</v>
       </c>
       <c r="D146" s="2">
@@ -4989,15 +5437,18 @@
       <c r="G146">
         <v>10</v>
       </c>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" s="1">
         <v>143</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C147" s="8">
+        <v>159</v>
+      </c>
+      <c r="C147" s="9">
         <v>914998398900</v>
       </c>
       <c r="D147" s="2">
@@ -5012,15 +5463,18 @@
       <c r="G147">
         <v>10</v>
       </c>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="H147" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" s="1">
         <v>144</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C148" s="8">
+        <v>160</v>
+      </c>
+      <c r="C148" s="9">
         <v>969898302800</v>
       </c>
       <c r="D148" s="2">
@@ -5035,15 +5489,18 @@
       <c r="G148">
         <v>10</v>
       </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="1">
         <v>145</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C149" s="8">
+        <v>161</v>
+      </c>
+      <c r="C149" s="9">
         <v>1028092201000</v>
       </c>
       <c r="D149" s="2">
@@ -5058,15 +5515,18 @@
       <c r="G149">
         <v>10</v>
       </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="1">
         <v>146</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C150" s="8">
+        <v>162</v>
+      </c>
+      <c r="C150" s="9">
         <v>1089777733100</v>
       </c>
       <c r="D150" s="2">
@@ -5081,15 +5541,18 @@
       <c r="G150">
         <v>10</v>
       </c>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="1">
         <v>147</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C151" s="8">
+        <v>163</v>
+      </c>
+      <c r="C151" s="9">
         <v>1155164397100</v>
       </c>
       <c r="D151" s="2">
@@ -5104,15 +5567,18 @@
       <c r="G151">
         <v>10</v>
       </c>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="H151" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="1">
         <v>148</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C152" s="8">
+        <v>164</v>
+      </c>
+      <c r="C152" s="9">
         <v>1224474260900</v>
       </c>
       <c r="D152" s="2">
@@ -5127,15 +5593,18 @@
       <c r="G152">
         <v>10</v>
       </c>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="H152" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" s="1">
         <v>149</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C153" s="8">
+        <v>165</v>
+      </c>
+      <c r="C153" s="9">
         <v>1297942716600</v>
       </c>
       <c r="D153" s="2">
@@ -5150,15 +5619,18 @@
       <c r="G153">
         <v>10</v>
       </c>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="H153" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="1">
         <v>150</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C154" s="8">
+        <v>166</v>
+      </c>
+      <c r="C154" s="9">
         <v>1375819279600</v>
       </c>
       <c r="D154" s="2">
@@ -5173,15 +5645,18 @@
       <c r="G154">
         <v>10</v>
       </c>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" s="1">
         <v>151</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C155" s="8">
+        <v>167</v>
+      </c>
+      <c r="C155" s="9">
         <v>1458368436400</v>
       </c>
       <c r="D155" s="2">
@@ -5196,15 +5671,18 @@
       <c r="G155">
         <v>10</v>
       </c>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="H155" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156" s="1">
         <v>152</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C156" s="8">
+        <v>168</v>
+      </c>
+      <c r="C156" s="9">
         <v>1545870542600</v>
       </c>
       <c r="D156" s="2">
@@ -5219,15 +5697,18 @@
       <c r="G156">
         <v>10</v>
       </c>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" s="1">
         <v>153</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C157" s="8">
+        <v>169</v>
+      </c>
+      <c r="C157" s="9">
         <v>1638622775200</v>
       </c>
       <c r="D157" s="2">
@@ -5242,15 +5723,18 @@
       <c r="G157">
         <v>10</v>
       </c>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158" s="1">
         <v>154</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C158" s="8">
+        <v>170</v>
+      </c>
+      <c r="C158" s="9">
         <v>1736940141700</v>
       </c>
       <c r="D158" s="2">
@@ -5265,15 +5749,18 @@
       <c r="G158">
         <v>10</v>
       </c>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" s="1">
         <v>155</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C159" s="8">
+        <v>171</v>
+      </c>
+      <c r="C159" s="9">
         <v>1841156550200</v>
       </c>
       <c r="D159" s="2">
@@ -5288,15 +5775,18 @@
       <c r="G159">
         <v>10</v>
       </c>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" s="1">
         <v>156</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C160" s="8">
+        <v>172</v>
+      </c>
+      <c r="C160" s="9">
         <v>1951625943200</v>
       </c>
       <c r="D160" s="2">
@@ -5311,15 +5801,18 @@
       <c r="G160">
         <v>10</v>
       </c>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="H160" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" s="1">
         <v>157</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C161" s="8">
+        <v>173</v>
+      </c>
+      <c r="C161" s="9">
         <v>2068723499800</v>
       </c>
       <c r="D161" s="2">
@@ -5334,15 +5827,18 @@
       <c r="G161">
         <v>10</v>
       </c>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="1">
         <v>158</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C162" s="8">
+        <v>174</v>
+      </c>
+      <c r="C162" s="9">
         <v>2192846909800</v>
       </c>
       <c r="D162" s="2">
@@ -5357,15 +5853,18 @@
       <c r="G162">
         <v>10</v>
       </c>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" s="1">
         <v>159</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C163" s="8">
+        <v>175</v>
+      </c>
+      <c r="C163" s="9">
         <v>2324417724400</v>
       </c>
       <c r="D163" s="2">
@@ -5380,15 +5879,18 @@
       <c r="G163">
         <v>10</v>
       </c>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" s="1">
         <v>160</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C164" s="8">
+        <v>176</v>
+      </c>
+      <c r="C164" s="9">
         <v>2463882787900</v>
       </c>
       <c r="D164" s="2">
@@ -5403,15 +5905,18 @@
       <c r="G164">
         <v>10</v>
       </c>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="H164" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" s="1">
         <v>161</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C165" s="8">
+        <v>177</v>
+      </c>
+      <c r="C165" s="9">
         <v>2562438099400</v>
       </c>
       <c r="D165" s="2">
@@ -5426,15 +5931,18 @@
       <c r="G165">
         <v>10</v>
       </c>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="H165" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" s="1">
         <v>162</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C166" s="8">
+        <v>178</v>
+      </c>
+      <c r="C166" s="9">
         <v>2664935623400</v>
       </c>
       <c r="D166" s="2">
@@ -5449,15 +5957,18 @@
       <c r="G166">
         <v>10</v>
       </c>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H166" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" s="1">
         <v>163</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C167" s="8">
+        <v>179</v>
+      </c>
+      <c r="C167" s="9">
         <v>2771533048300</v>
       </c>
       <c r="D167" s="2">
@@ -5472,15 +5983,18 @@
       <c r="G167">
         <v>10</v>
       </c>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="H167" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="1">
         <v>164</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C168" s="8">
+        <v>180</v>
+      </c>
+      <c r="C168" s="9">
         <v>2882394370200</v>
       </c>
       <c r="D168" s="2">
@@ -5495,15 +6009,18 @@
       <c r="G168">
         <v>10</v>
       </c>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="H168" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="1">
         <v>165</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C169" s="8">
+        <v>181</v>
+      </c>
+      <c r="C169" s="9">
         <v>2997690145000</v>
       </c>
       <c r="D169" s="2">
@@ -5518,15 +6035,18 @@
       <c r="G169">
         <v>10</v>
       </c>
-    </row>
-    <row r="170" spans="1:7">
+      <c r="H169" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="1">
         <v>166</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C170" s="8">
+        <v>182</v>
+      </c>
+      <c r="C170" s="9">
         <v>3117597750800</v>
       </c>
       <c r="D170" s="2">
@@ -5541,15 +6061,18 @@
       <c r="G170">
         <v>10</v>
       </c>
-    </row>
-    <row r="171" spans="1:7">
+      <c r="H170" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="1">
         <v>167</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C171" s="8">
+        <v>183</v>
+      </c>
+      <c r="C171" s="9">
         <v>3242301660800</v>
       </c>
       <c r="D171" s="2">
@@ -5564,15 +6087,18 @@
       <c r="G171">
         <v>10</v>
       </c>
-    </row>
-    <row r="172" spans="1:7">
+      <c r="H171" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="1">
         <v>168</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C172" s="8">
+        <v>184</v>
+      </c>
+      <c r="C172" s="9">
         <v>3371993727200</v>
       </c>
       <c r="D172" s="2">
@@ -5587,15 +6113,18 @@
       <c r="G172">
         <v>10</v>
       </c>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="H172" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="1">
         <v>169</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C173" s="8">
+        <v>185</v>
+      </c>
+      <c r="C173" s="9">
         <v>3506873476300</v>
       </c>
       <c r="D173" s="2">
@@ -5610,15 +6139,18 @@
       <c r="G173">
         <v>10</v>
       </c>
-    </row>
-    <row r="174" spans="1:7">
+      <c r="H173" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" s="1">
         <v>170</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C174" s="8">
+        <v>186</v>
+      </c>
+      <c r="C174" s="9">
         <v>3647148415400</v>
       </c>
       <c r="D174" s="2">
@@ -5633,15 +6165,18 @@
       <c r="G174">
         <v>10</v>
       </c>
-    </row>
-    <row r="175" spans="1:7">
+      <c r="H174" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175" s="1">
         <v>171</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C175" s="8">
+        <v>187</v>
+      </c>
+      <c r="C175" s="9">
         <v>3720091383700</v>
       </c>
       <c r="D175" s="2">
@@ -5656,15 +6191,18 @@
       <c r="G175">
         <v>10</v>
       </c>
-    </row>
-    <row r="176" spans="1:7">
+      <c r="H175" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="1">
         <v>172</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C176" s="8">
+        <v>188</v>
+      </c>
+      <c r="C176" s="9">
         <v>3794493211400</v>
       </c>
       <c r="D176" s="2">
@@ -5679,15 +6217,18 @@
       <c r="G176">
         <v>10</v>
       </c>
-    </row>
-    <row r="177" spans="1:7">
+      <c r="H176" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" s="1">
         <v>173</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C177" s="8">
+        <v>189</v>
+      </c>
+      <c r="C177" s="9">
         <v>3870383075600</v>
       </c>
       <c r="D177" s="2">
@@ -5702,15 +6243,18 @@
       <c r="G177">
         <v>10</v>
       </c>
-    </row>
-    <row r="178" spans="1:7">
+      <c r="H177" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" s="1">
         <v>174</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C178" s="8">
+        <v>190</v>
+      </c>
+      <c r="C178" s="9">
         <v>3947790737100</v>
       </c>
       <c r="D178" s="2">
@@ -5725,15 +6269,18 @@
       <c r="G178">
         <v>10</v>
       </c>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="H178" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" s="1">
         <v>175</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C179" s="8">
+        <v>191</v>
+      </c>
+      <c r="C179" s="9">
         <v>4026746551800</v>
       </c>
       <c r="D179" s="2">
@@ -5748,15 +6295,18 @@
       <c r="G179">
         <v>10</v>
       </c>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="H179" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" s="1">
         <v>176</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C180" s="8">
+        <v>192</v>
+      </c>
+      <c r="C180" s="9">
         <v>4107281482800</v>
       </c>
       <c r="D180" s="2">
@@ -5771,15 +6321,18 @@
       <c r="G180">
         <v>10</v>
       </c>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="H180" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" s="1">
         <v>177</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C181" s="8">
+        <v>193</v>
+      </c>
+      <c r="C181" s="9">
         <v>4189427112500</v>
       </c>
       <c r="D181" s="2">
@@ -5794,15 +6347,18 @@
       <c r="G181">
         <v>10</v>
       </c>
-    </row>
-    <row r="182" spans="1:7">
+      <c r="H181" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" s="1">
         <v>178</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C182" s="8">
+        <v>194</v>
+      </c>
+      <c r="C182" s="9">
         <v>4273215654800</v>
       </c>
       <c r="D182" s="2">
@@ -5817,15 +6373,18 @@
       <c r="G182">
         <v>10</v>
       </c>
-    </row>
-    <row r="183" spans="1:7">
+      <c r="H182" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" s="1">
         <v>179</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C183" s="8">
+        <v>195</v>
+      </c>
+      <c r="C183" s="9">
         <v>4358679967900</v>
       </c>
       <c r="D183" s="2">
@@ -5840,15 +6399,18 @@
       <c r="G183">
         <v>10</v>
       </c>
-    </row>
-    <row r="184" spans="1:7">
+      <c r="H183" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" s="1">
         <v>180</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C184" s="8">
+        <v>196</v>
+      </c>
+      <c r="C184" s="9">
         <v>4445853567300</v>
       </c>
       <c r="D184" s="2">
@@ -5863,15 +6425,18 @@
       <c r="G184">
         <v>10</v>
       </c>
-    </row>
-    <row r="185" spans="1:7">
+      <c r="H184" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" s="1">
         <v>181</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C185" s="8">
+        <v>197</v>
+      </c>
+      <c r="C185" s="9">
         <v>4534770638600</v>
       </c>
       <c r="D185" s="2">
@@ -5886,15 +6451,18 @@
       <c r="G185">
         <v>10</v>
       </c>
-    </row>
-    <row r="186" spans="1:7">
+      <c r="H185" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" s="1">
         <v>182</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C186" s="8">
+        <v>198</v>
+      </c>
+      <c r="C186" s="9">
         <v>4625466051400</v>
       </c>
       <c r="D186" s="2">
@@ -5909,15 +6477,18 @@
       <c r="G186">
         <v>10</v>
       </c>
-    </row>
-    <row r="187" spans="1:7">
+      <c r="H186" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" s="1">
         <v>183</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C187" s="8">
+        <v>199</v>
+      </c>
+      <c r="C187" s="9">
         <v>4717975372400</v>
       </c>
       <c r="D187" s="2">
@@ -5932,15 +6503,18 @@
       <c r="G187">
         <v>10</v>
       </c>
-    </row>
-    <row r="188" spans="1:7">
+      <c r="H187" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="1">
         <v>184</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C188" s="8">
+        <v>200</v>
+      </c>
+      <c r="C188" s="9">
         <v>4812334879800</v>
       </c>
       <c r="D188" s="2">
@@ -5955,15 +6529,18 @@
       <c r="G188">
         <v>10</v>
       </c>
-    </row>
-    <row r="189" spans="1:7">
+      <c r="H188" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" s="1">
         <v>185</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C189" s="8">
+        <v>201</v>
+      </c>
+      <c r="C189" s="9">
         <v>4908581577400</v>
       </c>
       <c r="D189" s="2">
@@ -5978,15 +6555,18 @@
       <c r="G189">
         <v>10</v>
       </c>
-    </row>
-    <row r="190" spans="1:7">
+      <c r="H189" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" s="1">
         <v>186</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C190" s="8">
+        <v>202</v>
+      </c>
+      <c r="C190" s="9">
         <v>5006753208900</v>
       </c>
       <c r="D190" s="2">
@@ -6001,15 +6581,18 @@
       <c r="G190">
         <v>10</v>
       </c>
-    </row>
-    <row r="191" spans="1:7">
+      <c r="H190" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" s="1">
         <v>187</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C191" s="8">
+        <v>203</v>
+      </c>
+      <c r="C191" s="9">
         <v>5106888273100</v>
       </c>
       <c r="D191" s="2">
@@ -6024,15 +6607,18 @@
       <c r="G191">
         <v>10</v>
       </c>
-    </row>
-    <row r="192" spans="1:7">
+      <c r="H191" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" s="1">
         <v>188</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C192" s="8">
+        <v>204</v>
+      </c>
+      <c r="C192" s="9">
         <v>5209026038600</v>
       </c>
       <c r="D192" s="2">
@@ -6047,15 +6633,18 @@
       <c r="G192">
         <v>10</v>
       </c>
-    </row>
-    <row r="193" spans="1:7">
+      <c r="H192" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" s="1">
         <v>189</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C193" s="8">
+        <v>205</v>
+      </c>
+      <c r="C193" s="9">
         <v>5313206559400</v>
       </c>
       <c r="D193" s="2">
@@ -6070,15 +6659,18 @@
       <c r="G193">
         <v>10</v>
       </c>
-    </row>
-    <row r="194" spans="1:7">
+      <c r="H193" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" s="1">
         <v>190</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C194" s="8">
+        <v>206</v>
+      </c>
+      <c r="C194" s="9">
         <v>5419470690600</v>
       </c>
       <c r="D194" s="2">
@@ -6093,15 +6685,18 @@
       <c r="G194">
         <v>10</v>
       </c>
-    </row>
-    <row r="195" spans="1:7">
+      <c r="H194" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" s="1">
         <v>191</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C195" s="8">
+        <v>207</v>
+      </c>
+      <c r="C195" s="9">
         <v>5527860104400</v>
       </c>
       <c r="D195" s="2">
@@ -6116,15 +6711,18 @@
       <c r="G195">
         <v>10</v>
       </c>
-    </row>
-    <row r="196" spans="1:7">
+      <c r="H195" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" s="1">
         <v>192</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C196" s="8">
+        <v>208</v>
+      </c>
+      <c r="C196" s="9">
         <v>5638417306500</v>
       </c>
       <c r="D196" s="2">
@@ -6139,15 +6737,18 @@
       <c r="G196">
         <v>10</v>
       </c>
-    </row>
-    <row r="197" spans="1:7">
+      <c r="H196" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197" s="1">
         <v>193</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C197" s="8">
+        <v>209</v>
+      </c>
+      <c r="C197" s="9">
         <v>5751185652600</v>
       </c>
       <c r="D197" s="2">
@@ -6162,15 +6763,18 @@
       <c r="G197">
         <v>10</v>
       </c>
-    </row>
-    <row r="198" spans="1:7">
+      <c r="H197" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" s="1">
         <v>194</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C198" s="8">
+        <v>210</v>
+      </c>
+      <c r="C198" s="9">
         <v>5866209365700</v>
       </c>
       <c r="D198" s="2">
@@ -6185,15 +6789,18 @@
       <c r="G198">
         <v>10</v>
       </c>
-    </row>
-    <row r="199" spans="1:7">
+      <c r="H198" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" s="1">
         <v>195</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C199" s="8">
+        <v>211</v>
+      </c>
+      <c r="C199" s="9">
         <v>5983533553000</v>
       </c>
       <c r="D199" s="2">
@@ -6208,15 +6815,18 @@
       <c r="G199">
         <v>10</v>
       </c>
-    </row>
-    <row r="200" spans="1:7">
+      <c r="H199" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" s="1">
         <v>196</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C200" s="8">
+        <v>212</v>
+      </c>
+      <c r="C200" s="9">
         <v>6103204224100</v>
       </c>
       <c r="D200" s="2">
@@ -6231,15 +6841,18 @@
       <c r="G200">
         <v>10</v>
       </c>
-    </row>
-    <row r="201" spans="1:7">
+      <c r="H200" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" s="1">
         <v>197</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C201" s="8">
+        <v>213</v>
+      </c>
+      <c r="C201" s="9">
         <v>6225268308600</v>
       </c>
       <c r="D201" s="2">
@@ -6254,15 +6867,18 @@
       <c r="G201">
         <v>10</v>
       </c>
-    </row>
-    <row r="202" spans="1:7">
+      <c r="H201" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" s="1">
         <v>198</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C202" s="8">
+        <v>214</v>
+      </c>
+      <c r="C202" s="9">
         <v>6349773674800</v>
       </c>
       <c r="D202" s="2">
@@ -6277,15 +6893,18 @@
       <c r="G202">
         <v>10</v>
       </c>
-    </row>
-    <row r="203" spans="1:7">
+      <c r="H202" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" s="1">
         <v>199</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C203" s="8">
+        <v>215</v>
+      </c>
+      <c r="C203" s="9">
         <v>6476769148300</v>
       </c>
       <c r="D203" s="2">
@@ -6300,15 +6919,18 @@
       <c r="G203">
         <v>10</v>
       </c>
-    </row>
-    <row r="204" spans="1:7">
+      <c r="H203" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204" s="1">
         <v>200</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C204" s="8"/>
+        <v>216</v>
+      </c>
+      <c r="C204" s="9"/>
       <c r="D204" s="2">
         <v>0</v>
       </c>
@@ -6320,6 +6942,9 @@
       </c>
       <c r="G204">
         <v>10</v>
+      </c>
+      <c r="H204" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
